--- a/30_day_dsa_plan.xlsx
+++ b/30_day_dsa_plan.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/narendya/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340DA159-270E-E942-A4ED-D9B3606132DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2A0AD2-F557-8946-B812-D89516A416FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30-Day DSA Plan" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="134">
   <si>
     <t>Day</t>
   </si>
@@ -251,6 +252,177 @@
   </si>
   <si>
     <t>Mock Interview</t>
+  </si>
+  <si>
+    <t>Link 1</t>
+  </si>
+  <si>
+    <t>Link 2</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/two-sum/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-subarray/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/reverse-string/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/monotonic-array/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>First Unique Character</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/move-zeroes/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/rotate-array/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/third-maximum-number/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/missing-number/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-the-duplicate-number/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/best-time-to-buy-and-sell-stock/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/contains-duplicate/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-anagram/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-all-anagrams-in-a-string/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/reverse-words-in-a-string/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-palindrome/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-palindrome-ii/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/group-anagrams/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/intersection-of-two-arrays/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-consecutive-sequence/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subarray-sum-equals-k/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/sliding-window-maximum/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/reverse-linked-list/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/linked-list-cycle/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/merge-two-sorted-lists/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/remove-nth-node-from-end-of-list/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/palindrome-linked-list/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/fibonacci-number/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subsets/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/permutations/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/combination-sum/</t>
+  </si>
+  <si>
+    <t>Subsets II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/subsets-ii/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/word-search/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/n-queens/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-parentheses/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/min-stack/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/implement-queue-using-stacks/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/binary-search/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/search-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/binary-tree-inorder-traversal/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-tree/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/diameter-of-binary-tree/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/top-k-frequent-elements/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/kth-largest-element-in-an-array/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-islands/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/network-delay-time/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/cheapest-flights-within-k-stops/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problem-list/top-interview-questions/</t>
   </si>
 </sst>
 </file>
@@ -1050,6 +1222,639 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEE4F11-7E36-724B-89AE-E7CD7A3D46AC}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="7" width="21.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{825c952f-1947-4719-99e7-7bc5a76060a8}" enabled="1" method="Standard" siteId="{4e2c6054-71cb-48f1-bd6c-3a9705aca71b}" contentBits="3" removed="0"/>
